--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0196.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0196.xlsx
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Nhưng giờ ta vẫn còn vài việc khác cần giải quyết...</t>
+          <t>Nhưng giờ tao vẫn còn vài việc khác cần giải quyết...</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Cậu cũng biết múa lân quan trọng với người dân ở Kim Châu đến thế nào! Không thể từ chối được.</t>
+          <t>Cậu cũng biết múa lân quan trọng với người dân ở Jinzhou đến thế nào! Không thể từ chối được.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Được! Cậu vừa cứu mạng ta. Ta sẽ kể cho cậu tất cả những gì ta nhớ được!</t>
+          <t>Được! Cậu vừa cứu mạng tao. Tao sẽ kể cho cậu tất cả những gì tao nhớ được!</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hừm, xin lỗi, nhưng chuyện này ta chẳng nhớ tý gì cả...</t>
+          <t>Hừm, xin lỗi, nhưng chuyện này tao chẳng nhớ tý gì cả...</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Chỗ cắm trại gần cái cây gãy, có thể nhìn thấy từ tháp canh... Ta biết chỗ đó rồi.</t>
+          <t>Chỗ cắm trại gần cái cây gãy, có thể nhìn thấy từ tháp canh... Tao biết chỗ đó rồi.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Ngươi chỉ là một con chó con thôi. Ngươi không biết thứ gì mới thực sự khiến người ta sợ hãi đâu...</t>
+          <t>Mày chỉ là một con chó con thôi. Mày không biết thứ gì mới thực sự khiến người ta sợ hãi đâu...</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Ui da... Ta cũng bực mình lắm đấy.</t>
+          <t>Ui da... Tao cũng bực mình lắm đấy.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Ta sẽ đi tìm Bắc Cực.</t>
+          <t>Tao sẽ đi tìm Bắc Cực.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Ta sẽ đi tìm bọn The Savages.</t>
+          <t>Tao sẽ đi tìm bọn The Savages.</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Ổn đấy. Bọn Savages cảnh giác lắm, nhưng ta còn rành vùng hoang dã hơn chúng. Ta sẽ lần theo dấu chúng.</t>
+          <t>Ổn đấy. Bọn Savages cảnh giác lắm, nhưng tao còn rành vùng hoang dã hơn chúng. Tao sẽ lần theo dấu chúng.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nhưng đó là giấc mơ thời thơ ấu của ta, nên tụi ta đã cãi nhau to...</t>
+          <t>Nhưng đó là giấc mơ thời thơ ấu của tao, nên tụi tao đã cãi nhau to...</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Ta biết... Âm thanh đó ta nghe rõ lắm rồi.</t>
+          <t>Tao biết... Âm thanh đó tao nghe rõ lắm rồi.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Nếu không chạy thoát được, có lẽ giờ ta đã thành bữa ăn của con Quái Thú Kêu Reng rồi...</t>
+          <t>Nếu không chạy thoát được, có lẽ giờ tao đã thành bữa ăn của con Quái Thú Kêu Reng rồi...</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tiếng chuông kêu to à? Hình như ta có nghe thấy gì đó giống thế, nhưng…</t>
+          <t>Tiếng chuông kêu to à? Hình như tao có nghe thấy gì đó giống thế, nhưng…</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Có lẽ ta không nên nhờ ngươi thêm lần nào nữa... nhưng Bei Ji đang gặp nguy, tình hình nguy cấp lắm, cần ngươi giúp đỡ.</t>
+          <t>Có lẽ tao không nên nhờ mày thêm lần nào nữa... nhưng Bei Ji đang gặp nguy, tình hình nguy cấp lắm, cần mày giúp đỡ.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Được thôi, ta tò mò chuyện gì đã xảy ra thật sự.</t>
+          <t>Được thôi, tao tò mò chuyện gì đã xảy ra thật sự.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Lingyang! Rover!</t>
+          <t>Lingyang! Vận Mệnh Giả!</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Ta chỉ muốn cho nó thấy... Nếu đứa em nhát gan như ta còn làm được, thì nó cũng làm được!</t>
+          <t>Tao chỉ muốn cho nó thấy... Nếu đứa em nhát gan như tao còn làm được, thì nó cũng làm được!</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo cậu quên mất lời yêu cầu múa lân của mình rồi à?</t>
+          <t>Đừng có mà bảo mày quên mất lời yêu cầu múa lân của mình rồi à?</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -18904,7 +18904,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Ra là vậy...</t>
+          <t>Ta hiểu rồi...</t>
         </is>
       </c>
     </row>
@@ -19359,7 +19359,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Ý bạn là gì?</t>
+          <t>Ý anh là sao?</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ta đến rồi! Ta đến rồi!</t>
+          <t>Tao đến rồi! Tao đến rồi!</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Sau đó ta nghe nói về Jingle Beast, nên ta đoán chắc đó là thứ đã tấn công ta.</t>
+          <t>Sau đó tao nghe nói về Jingle Beast, nên tao đoán chắc đó là thứ đã tấn công tao.</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Ta hứa, ta hứa mà. Để ta mời cậu cái gì đó như lời xin lỗi chân thành.</t>
+          <t>Tao hứa, tao hứa mà. Để tao mời cậu cái gì đó như lời xin lỗi chân thành.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Cậu làm ta đỏ mặt rồi đấy, {PlayerName}...</t>
+          <t>Cậu làm tao đỏ mặt rồi đấy, {PlayerName}...</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Dù sao thì nghe cậu nói vậy ta cũng vui lắm rồi.</t>
+          <t>Dù sao thì nghe cậu nói vậy tao cũng vui lắm rồi.</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Cảm xúc không kiểm soát ở Cộng Hưởng Giả loài người có thể dẫn đến &lt;ano=Overclocking&gt;thảm họa&lt;/ano&gt;. Ở loài thú còn nguy hiểm hơn, vì chúng chỉ biết nghe theo bản năng.</t>
+          <t>Cảm xúc không kiểm soát ở Resonator loài người có thể dẫn đến &lt;ano=Overclocking&gt;thảm họa&lt;/ano&gt;. Ở loài thú còn nguy hiểm hơn, vì chúng chỉ biết nghe theo bản năng.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Và... Ta có nghe mấy nhà khảo cổ học nói về một giả thuyết thú vị...</t>
+          <t>Và... Tao có nghe mấy nhà khảo cổ học nói về một giả thuyết thú vị...</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Ôi, {PlayerName}?! Sao-sao cậu lại ở đây thế?!</t>
+          <t>Ôi, {PlayerName}?! Sao-sao mày lại ở đây thế?!</t>
         </is>
       </c>
     </row>
@@ -28719,7 +28719,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Không biết nữa. Chân tự đưa ta đến đây thôi.</t>
+          <t>Không biết nữa. Chân tự đưa tao đến đây thôi.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Cảm ơn {PlayerName}! Khu rừng này và em sẽ không bao giờ quên sự giúp đỡ của cậu!</t>
+          <t>Cảm ơn {PlayerName}! Khu rừng này và em sẽ không bao giờ quên sự giúp đỡ của bạn!</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Được thôi, ta vui vẻ làm theo ý cậu mà.</t>
+          <t>Được thôi, tao vui vẻ làm theo ý cậu mà.</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Hello!</t>
+          <t>Chào cậu!</t>
         </is>
       </c>
     </row>
